--- a/forms/trg/Formulir_TRG_house-sett.xlsx
+++ b/forms/trg/Formulir_TRG_house-sett.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
+          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+          <t>Belum ada artikel tercatat di situs. Mohon cantumkan riset terbaik di lembar TRG &amp; Riset.</t>
         </is>
       </c>
     </row>
@@ -710,126 +710,114 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Belum ada artikel tercatat di situs. Mohon cantumkan riset terbaik di lembar TRG &amp; Riset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
           <t>Belum ada proyek riset tercatat di situs.</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>COUNTA(Anggota!B5:B33)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B28" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B29" s="8">
-        <f>IF(B27=0,0,B28/B27)</f>
+      <c r="B28" s="8">
+        <f>IF(B26=0,0,B27/B26)</f>
         <v/>
       </c>
     </row>
@@ -844,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -949,22 +937,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Suci Anugrah Yanti, S.T., M.Si.</t>
+          <t>Prof. Dr. Ir. Mimi Arifin, M. Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Urban and Regional Planning Department, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Urban Planning and Design</t>
+          <t>Housing and Settlement Planning</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -986,12 +970,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Sri Aliah Ekawati, S.T., M.T</t>
+          <t>Suci Anugrah Yanti, S.T., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1001,7 +985,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Waterfront City Planning and Development</t>
+          <t>Urban Planning and Design</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -1023,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Gafar Lakatupa, ST., M. Eng</t>
+          <t>Sri Aliah Ekawati, S.T., M.T</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1038,7 +1022,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Housing and Settlement Planning</t>
+          <t>Waterfront City Planning and Development</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1060,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Marly Valenti Patandianan, ST.,MT.,Ph.D</t>
+          <t>Gafar Lakatupa, ST., M. Eng</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1075,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Regional Planning, Tourism, and Disaster Mitigation</t>
+          <t>Housing and Settlement Planning</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1097,12 +1081,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr.-Ing. Venny Veronica Natalia, ST.,MT</t>
+          <t>Marly Valenti Patandianan, ST.,MT.,Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1112,7 +1096,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Infrastructure and Transportation Planning</t>
+          <t>Regional Planning, Tourism, and Disaster Mitigation</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1134,12 +1118,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wiwik Wahidah Osman, ST., MT</t>
+          <t>Dr.-Ing. Venny Veronica Natalia, ST.,MT</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1149,7 +1133,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Housing and Settlement Planning</t>
+          <t>Infrastructure and Transportation Planning</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1171,20 +1155,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Peter Aning Anak Tedong</t>
+          <t>Dr. Wiwik Wahidah Osman, ST., MT</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Malaya</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>Urban and Regional Planning Department, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Housing and Settlement Planning</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1204,17 +1192,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Ts Dr. Noor Aimran Bin Samsudin</t>
+          <t>Prof. Dr. Peter Aning Anak Tedong</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi Malaysia</t>
+          <t>Universiti Malaya</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1237,20 +1225,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fitrawan Umar, S.T., M.Sc.</t>
+          <t>Ts Dr. Noor Aimran Bin Samsudin</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Badan Riset dan Inovasi Nasional</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Universiti Teknologi Malaysia</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1270,20 +1258,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Aris Alimuddin</t>
+          <t>Dr. Fitrawan Umar, S.T., M.Sc.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Urban and Regional Planning Department, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1303,12 +1291,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Imriyanti</t>
+          <t>Aris Alimuddin</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1336,12 +1324,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>A.Nada Zahirah</t>
+          <t>Imriyanti</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1369,12 +1357,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Maghfirah Maharani</t>
+          <t>A.Nada Zahirah</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1402,12 +1390,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi Budjang</t>
+          <t>Maghfirah Maharani</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1435,12 +1423,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Andi Annisa Harum Mawladri</t>
+          <t>Ahmad Fauzi Budjang</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1468,12 +1456,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Muflih Hamdi</t>
+          <t>Andi Annisa Harum Mawladri</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1499,10 +1487,26 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Muflih Hamdi</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Urban and Regional Planning Department, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the official website of the Corporate Auditing Research Group . Our research group members also have a wealth of advisory and consultative experience and a demonstrated commitment to providing objective, technical, and evidence-driven advice.</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -1510,7 +1514,11 @@
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1699,15 +1707,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
